--- a/现有全部对照品目录.xlsx
+++ b/现有全部对照品目录.xlsx
@@ -1,212 +1,46 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\新建文件夹 (2)\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74892FE6-F30A-4199-8F50-B91D26843BB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="56">
-  <si>
-    <t>序号</t>
-  </si>
-  <si>
-    <t>对照品中文名称</t>
-  </si>
-  <si>
-    <t>对照品中文批号Chp</t>
-  </si>
-  <si>
-    <t>对照品英文名称EP</t>
-  </si>
-  <si>
-    <t>对照品英文批号EP</t>
-  </si>
-  <si>
-    <t>对照品英文名称USP</t>
-  </si>
-  <si>
-    <t>对照品英文批号USP</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>艾普拉唑磺酰化物</t>
-  </si>
-  <si>
-    <t>100909-202002</t>
-  </si>
-  <si>
-    <t>Brivaracetam CRS</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>水杨酸</t>
-  </si>
-  <si>
-    <t>100106-202106</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>艾普拉唑</t>
-  </si>
-  <si>
-    <t>100908-202403</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>盐酸坦索罗辛</t>
-  </si>
-  <si>
-    <t>100688-202103</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>甲磺酸多沙唑嗪</t>
-  </si>
-  <si>
-    <t>100566-202403</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>羟苯丙酯</t>
-  </si>
-  <si>
-    <t>100444-202306</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>伊曲康唑</t>
-  </si>
-  <si>
-    <t>100631-201402</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>伊曲康唑杂质A</t>
-  </si>
-  <si>
-    <t>130686-201501</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>伊曲康唑杂质B</t>
-  </si>
-  <si>
-    <t>130687-201501</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>伊曲康唑杂质C</t>
-  </si>
-  <si>
-    <t>130688-201501</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>伊曲康唑杂质D</t>
-  </si>
-  <si>
-    <t>130689-201501</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>伊曲康唑杂质E</t>
-  </si>
-  <si>
-    <t>130690-201501</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>伊曲康唑杂质F</t>
-  </si>
-  <si>
-    <t>130691-201501</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>伊曲康唑杂质G</t>
-  </si>
-  <si>
-    <t>130692-201501</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-</sst>
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+  <numFmts count="1">
+    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+  </numFmts>
+  <fonts count="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -231,21 +65,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -570,234 +396,222 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G21"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
-  <cols>
-    <col min="2" max="2" width="19.5" customWidth="1"/>
-    <col min="3" max="3" width="19.125" customWidth="1"/>
-    <col min="4" max="4" width="21" customWidth="1"/>
-    <col min="5" max="5" width="15.875" customWidth="1"/>
-  </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="14.25" x14ac:dyDescent="0.15">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
+    <row r="1">
+      <c r="A1" t="str">
+        <v>序号</v>
+      </c>
+      <c r="B1" t="str">
+        <v>对照品中文名称</v>
+      </c>
+      <c r="C1" t="str">
+        <v>对照品中文批号Chp</v>
+      </c>
+      <c r="D1" t="str">
+        <v>对照品英文名称EP</v>
+      </c>
+      <c r="E1" t="str">
+        <v>对照品英文批号EP</v>
+      </c>
+      <c r="F1" t="str">
+        <v>对照品英文名称USP</v>
+      </c>
+      <c r="G1" t="str">
+        <v>对照品英文批号USP</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="B2" t="str">
+        <v>艾普拉唑磺酰化物</v>
+      </c>
+      <c r="C2" t="str">
+        <v>100909-202002</v>
+      </c>
+      <c r="D2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="B3" t="str">
+        <v>水杨酸</v>
+      </c>
+      <c r="C3" t="str">
+        <v>100106-202106</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="B4" t="str">
+        <v>艾普拉唑</v>
+      </c>
+      <c r="C4" t="str">
+        <v>100908-202403</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="B5" t="str">
+        <v>盐酸坦索罗辛</v>
+      </c>
+      <c r="C5" t="str">
+        <v>100688-202103</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="B6" t="str">
+        <v>甲磺酸多沙唑嗪</v>
+      </c>
+      <c r="C6" t="str">
+        <v>100566-202403</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" ht="14.25" x14ac:dyDescent="0.15">
-      <c r="A2" t="s">
+      <c r="B7" t="str">
+        <v>羟苯丙酯</v>
+      </c>
+      <c r="C7" t="str">
+        <v>100444-202306</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
         <v>7</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B8" t="str">
+        <v>伊曲康唑</v>
+      </c>
+      <c r="C8" t="str">
+        <v>100631-201402</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
         <v>8</v>
       </c>
-      <c r="C2" t="s">
+      <c r="B9" t="str">
+        <v>伊曲康唑杂质A</v>
+      </c>
+      <c r="C9" t="str">
+        <v>130686-201501</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
         <v>9</v>
       </c>
-      <c r="D2" t="s">
+      <c r="B10" t="str">
+        <v>伊曲康唑杂质B</v>
+      </c>
+      <c r="C10" t="str">
+        <v>130687-201501</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
         <v>10</v>
       </c>
-      <c r="E2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="14.25" x14ac:dyDescent="0.15">
-      <c r="A3" t="s">
+      <c r="B11" t="str">
+        <v>伊曲康唑杂质C</v>
+      </c>
+      <c r="C11" t="str">
+        <v>130688-201501</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
         <v>11</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B12" t="str">
+        <v>伊曲康唑杂质D</v>
+      </c>
+      <c r="C12" t="str">
+        <v>130689-201501</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
         <v>12</v>
       </c>
-      <c r="C3" t="s">
+      <c r="B13" t="str">
+        <v>伊曲康唑杂质E</v>
+      </c>
+      <c r="C13" t="str">
+        <v>130690-201501</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
         <v>13</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" ht="14.25" x14ac:dyDescent="0.15">
-      <c r="A4" t="s">
+      <c r="B14" t="str">
+        <v>伊曲康唑杂质F</v>
+      </c>
+      <c r="C14" t="str">
+        <v>130691-201501</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
         <v>14</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B15" t="str">
+        <v>伊曲康唑杂质G</v>
+      </c>
+      <c r="C15" t="str">
+        <v>130692-201501</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
         <v>15</v>
       </c>
-      <c r="C4" t="s">
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="14.25" x14ac:dyDescent="0.15">
-      <c r="A5" t="s">
+    <row r="18">
+      <c r="A18" t="str">
         <v>17</v>
       </c>
-      <c r="B5" t="s">
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
         <v>18</v>
       </c>
-      <c r="C5" t="s">
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="14.25" x14ac:dyDescent="0.15">
-      <c r="A6" t="s">
+    <row r="21">
+      <c r="A21" t="str">
         <v>20</v>
       </c>
-      <c r="B6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C6" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="14.25" x14ac:dyDescent="0.15">
-      <c r="A7" t="s">
-        <v>23</v>
-      </c>
-      <c r="B7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="14.25" x14ac:dyDescent="0.15">
-      <c r="A8" t="s">
-        <v>26</v>
-      </c>
-      <c r="B8" t="s">
-        <v>28</v>
-      </c>
-      <c r="C8" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="14.25" x14ac:dyDescent="0.15">
-      <c r="A9" t="s">
-        <v>27</v>
-      </c>
-      <c r="B9" t="s">
-        <v>31</v>
-      </c>
-      <c r="C9" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="14.25" x14ac:dyDescent="0.15">
-      <c r="A10" t="s">
-        <v>30</v>
-      </c>
-      <c r="B10" t="s">
-        <v>34</v>
-      </c>
-      <c r="C10" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="14.25" x14ac:dyDescent="0.15">
-      <c r="A11" t="s">
-        <v>33</v>
-      </c>
-      <c r="B11" t="s">
-        <v>37</v>
-      </c>
-      <c r="C11" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="14.25" x14ac:dyDescent="0.15">
-      <c r="A12" t="s">
-        <v>36</v>
-      </c>
-      <c r="B12" t="s">
-        <v>40</v>
-      </c>
-      <c r="C12" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="14.25" x14ac:dyDescent="0.15">
-      <c r="A13" t="s">
-        <v>39</v>
-      </c>
-      <c r="B13" t="s">
-        <v>43</v>
-      </c>
-      <c r="C13" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="14.25" x14ac:dyDescent="0.15">
-      <c r="A14" t="s">
-        <v>42</v>
-      </c>
-      <c r="B14" t="s">
-        <v>46</v>
-      </c>
-      <c r="C14" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="14.25" x14ac:dyDescent="0.15">
-      <c r="A15" t="s">
-        <v>45</v>
-      </c>
-      <c r="B15" t="s">
-        <v>49</v>
-      </c>
-      <c r="C15" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="14.25" x14ac:dyDescent="0.15">
-      <c r="A16" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" ht="14.25" x14ac:dyDescent="0.15">
-      <c r="A17" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" ht="14.25" x14ac:dyDescent="0.15">
-      <c r="A18" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" ht="14.25" x14ac:dyDescent="0.15">
-      <c r="A19" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" ht="14.25" x14ac:dyDescent="0.15">
-      <c r="A20" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" ht="14.25" x14ac:dyDescent="0.15">
-      <c r="A21" t="s">
-        <v>55</v>
-      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:G7 A17:G21 A8 D8:G8 A9:A15 D9:G15 A16 D16:G16" numberStoredAsText="1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G21"/>
   </ignoredErrors>
 </worksheet>
 </file>